--- a/Input/redaction_template.xlsx
+++ b/Input/redaction_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="179">
   <si>
     <t>condition</t>
   </si>
@@ -480,26 +480,6 @@
     <t>p13_neutre</t>
   </si>
   <si>
-    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } انخفض الرقم الاستدلالي للأثمان عند الاستهلاك
-ب {evol_non_alim_12mois} % مقارنة بشهر {lib_mois_courant } {annee_m12 } </t>
-  </si>
-  <si>
-    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a décru de {evol_non_alim_12mois}% par rapport à {lib_mois_courant} {annee_m12}</t>
-  </si>
-  <si>
-    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index decreased by {evol_non_alim_12mois}% compared to {lib_mois_courant} {annee_m12}</t>
-  </si>
-  <si>
-    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a augmenté de {evol_non_alim_12mois}% par rapport à {lib_mois_courant} {annee_m12}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } ارتفع الرقم الاستدلالي للأثمان عند الاستهلاك
-ب {evol_non_alim_12mois} % مقارنة بشهر {lib_mois_courant } {annee_m12 } </t>
-  </si>
-  <si>
-    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index increased by {evol_non_alim_12mois}% compared to {lib_mois_courant} {annee_m12}</t>
-  </si>
-  <si>
     <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index decreased stagnated compared to {lib_mois_courant} {annee_m12}</t>
   </si>
   <si>
@@ -523,6 +503,86 @@
   </si>
   <si>
     <t xml:space="preserve"> Évolution de la variation mensuelle (%) de l’indice des prix à la consommation</t>
+  </si>
+  <si>
+    <t>p16</t>
+  </si>
+  <si>
+    <t>p16_neutre</t>
+  </si>
+  <si>
+    <t>p16_moins</t>
+  </si>
+  <si>
+    <t>p16_plus</t>
+  </si>
+  <si>
+    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a augmenté de {evol_1mois}% par rapport à {lib_mois_m1} {annee_m1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } ارتفع الرقم الاستدلالي للأثمان عند الاستهلاك
+ب {evol_1mois} % مقارنة بشهر {lib_mois_m1} {annee_m1 } </t>
+  </si>
+  <si>
+    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index increased by {evol_1mois}% compared to {lib_mois_m1} {annee_m1}</t>
+  </si>
+  <si>
+    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a diminué de {evol_1mois}% par rapport à {lib_mois_m1} {annee_m1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } انخفظ الرقم الاستدلالي للأثمان عند الاستهلاك
+ب {evol_1mois} % مقارنة بشهر {lib_mois_m1} {annee_m1 } </t>
+  </si>
+  <si>
+    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index decreased by {evol_1mois}% compared to {lib_mois_m1} {annee_m1}</t>
+  </si>
+  <si>
+    <t>evol_1mois &lt; 0</t>
+  </si>
+  <si>
+    <t>evol_1mois &gt; 0</t>
+  </si>
+  <si>
+    <t>evol_1mois = 0</t>
+  </si>
+  <si>
+    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a gardé la même valeur par rapport à {lib_mois_m1} {annee_m1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } حافظ الرقم الاستدلالي للأثمان عند الاستهلاك
+على نفس القيمة مقارنة بشهر {lib_mois_m1 } {annee_m1 } </t>
+  </si>
+  <si>
+    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index decreased stagnated compared to {lib_mois_m1} {annee_m1}</t>
+  </si>
+  <si>
+    <t>evol_12mois &gt; 0</t>
+  </si>
+  <si>
+    <t>evol_12mois &lt; 0</t>
+  </si>
+  <si>
+    <t>evol_12mois = 0</t>
+  </si>
+  <si>
+    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a augmenté de {evol_12mois}% par rapport à {lib_mois_courant} {annee_m12}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } ارتفع الرقم الاستدلالي للأثمان عند الاستهلاك
+ب {evol_12mois} % مقارنة بشهر {lib_mois_courant } {annee_m12 } </t>
+  </si>
+  <si>
+    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index increased by {evol_12mois}% compared to {lib_mois_courant} {annee_m12}</t>
+  </si>
+  <si>
+    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index decreased by {evol_12mois}% compared to {lib_mois_courant} {annee_m12}</t>
+  </si>
+  <si>
+    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a décru de {evol_12mois}% par rapport à {lib_mois_courant} {annee_m12}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } انخفض الرقم الاستدلالي للأثمان عند الاستهلاك
+{evol_12mois} % مقارنة بشهر {lib_mois_courant } {annee_m12 } </t>
   </si>
 </sst>
 </file>
@@ -868,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -1447,16 +1507,16 @@
         <v>141</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="60">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="45">
       <c r="A31" s="1" t="s">
         <v>142</v>
       </c>
@@ -1464,19 +1524,19 @@
         <v>143</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="60">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="45">
       <c r="A32" s="1" t="s">
         <v>142</v>
       </c>
@@ -1484,16 +1544,16 @@
         <v>144</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>126</v>
+        <v>171</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45">
@@ -1504,33 +1564,93 @@
         <v>145</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30">
       <c r="A34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="45">
+      <c r="A35" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="45">
+      <c r="A36" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="45">
+      <c r="A37" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>158</v>
+      <c r="C37" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/Input/redaction_template.xlsx
+++ b/Input/redaction_template.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="187">
   <si>
     <t>condition</t>
   </si>
@@ -584,12 +584,56 @@
     <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } انخفض الرقم الاستدلالي للأثمان عند الاستهلاك
 {evol_12mois} % مقارنة بشهر {lib_mois_courant } {annee_m12 } </t>
   </si>
+  <si>
+    <t>p17</t>
+  </si>
+  <si>
+    <t>Indice des prix à la consommation de la {ville}: {lib_mois_courant}  {annee_courante} (base 2017: 100)</t>
+  </si>
+  <si>
+    <t>Consumer price index for the {ville}: {lib_mois_courant}  {annee_courante} (2017 base: 100)</t>
+  </si>
+  <si>
+    <t>الرقم الاستدلالي للأثمان عند الاستهلاك {ville} {lib_mois_courant } :{annee_courante } (أساس 2017:100)</t>
+  </si>
+  <si>
+    <t>p20</t>
+  </si>
+  <si>
+    <t>Source: High Commission for Planning, Department of Statistics - National consumer price survey</t>
+  </si>
+  <si>
+    <t>Source: Haut-Commissariat au Plan, Direction de la Statistique – Enquête Nationale sur les Prix à la Consommation.</t>
+  </si>
+  <si>
+    <r>
+      <t>المصدر</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="TimesNewRomanPS-BoldMT"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF8D4355"/>
+        <rFont val="TimesNewRomanPS-BoldMT"/>
+      </rPr>
+      <t>المندوبية السامية للتخطيط، مديرية الإحصاء -البحث الوطني حول الأثمان عند الاستهلاك</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,6 +658,18 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="TimesNewRomanPSMT"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF8D4355"/>
+      <name val="TimesNewRomanPS-BoldMT"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="TimesNewRomanPS-BoldMT"/>
     </font>
   </fonts>
   <fills count="2">
@@ -928,7 +984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1"/>
@@ -1651,6 +1707,40 @@
       </c>
       <c r="F37" s="1" t="s">
         <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="30">
+      <c r="A38" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="45">
+      <c r="A39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/Input/redaction_template.xlsx
+++ b/Input/redaction_template.xlsx
@@ -82,9 +82,6 @@
     <t>Sur un mois, l'indice des prix des produits alimentaires a augumenté de {evol_alim_1mois}% en {lib_mois_courant} {annee_courante} par rapport à  {lib_mois_m1} {annee_m1}</t>
   </si>
   <si>
-    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد ىالغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 } .{annee_m1 }</t>
-  </si>
-  <si>
     <t>The consumer price index experienced an increase of {evol_alim_1mois}% during the month of  {lib_mois_courant} {annee_courante} compared to the previous month.</t>
   </si>
   <si>
@@ -94,12 +91,6 @@
     <t>The consumer price index experienced a decrease of {evol_alim_1mois}% during the month of  {lib_mois_courant} {annee_courante} compared to the previous month.</t>
   </si>
   <si>
-    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد ىالغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  .</t>
-  </si>
-  <si>
-    <t>على المستوى الشهري انخفض الرقم الاستدلالي للمواد ىالغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 }  .{annee_m1 }</t>
-  </si>
-  <si>
     <t>variation_mensuelle_ipc_alim* nonalim &lt; 0</t>
   </si>
   <si>
@@ -257,17 +248,6 @@
   </si>
   <si>
     <t>The monthly variation in the non-food index stagnated following stagnation in prices in the following divisions: {liste_div_non_alim_neutre}.</t>
-  </si>
-  <si>
-    <t>la variation mensuelle de l'indice des produits non alimentaires a accru de  {evol_non_alim_1mois}% en raison de la hausse des prix des divisions suivantes : {liste_div_non_alim_plus}. Aussi la baisse {liste_div_non_alim_moins} et la stagnation des indices des autres
-divisions n’ont pas impacté l'évolution générale.</t>
-  </si>
-  <si>
-    <t>la variation mensuelle de l'indice des produits non alimentaires a decru de  {evol_non_alim_1mois}% en raison de la baisse des prix des divisions suivantes: {liste_div_non_alim_moins}. Aussi la hausse {liste_div_non_alim_plus} et la stagnation des indices des autres
-divisions n’ont pas impacté l'évolution générale.</t>
-  </si>
-  <si>
-    <t>La variation mensuelle de l'indice des produits non alimentaires a stagné suite à la stagnation des prix des divisions suivantes: {liste_div_non_alim_neutre}.Aussi la hausse {liste_div_non_alim_plus} et la baisse {liste_div_non_alim_moins} n’ont pas impacté l'évolution générale.</t>
   </si>
   <si>
     <t>في حين،</t>
@@ -627,6 +607,26 @@
       </rPr>
       <t>المندوبية السامية للتخطيط، مديرية الإحصاء -البحث الوطني حول الأثمان عند الاستهلاك</t>
     </r>
+  </si>
+  <si>
+    <t>la variation mensuelle de l'indice des produits non alimentaires a accru de  {evol_non_alim_1mois}% en raison de la hausse des prix des divisions suivantes : {liste_div_non_alim_plus}. Aussi la baisse des prix {liste_div_non_alim_moins} et la stagnation des indices des autres
+divisions n’ont pas impacté l'évolution générale.</t>
+  </si>
+  <si>
+    <t>la variation mensuelle de l'indice des produits non alimentaires a decru de  {evol_non_alim_1mois}% en raison de la baisse des prix des divisions suivantes: {liste_div_non_alim_moins}. Aussi la hausse hausse des prix {liste_div_non_alim_plus} et la stagnation des indices des autres
+divisions n’ont pas impacté l'évolution générale.</t>
+  </si>
+  <si>
+    <t>La variation mensuelle de l'indice des produits non alimentaires a stagné suite à la stagnation des prix des divisions suivantes: {liste_div_non_alim_neutre}.Aussi la hausse des prix {liste_div_non_alim_plus} et la baisse des prix {liste_div_non_alim_moins} n’ont pas impacté l'évolution générale.</t>
+  </si>
+  <si>
+    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد الغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 } .{annee_m1 }</t>
+  </si>
+  <si>
+    <t>على المستوى الشهري انخفض الرقم الاستدلالي للمواد الغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 }  .{annee_m1 }</t>
+  </si>
+  <si>
+    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد الغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  .</t>
   </si>
 </sst>
 </file>
@@ -976,7 +976,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -998,7 +998,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1018,50 +1018,50 @@
     </row>
     <row r="2" spans="1:6" ht="45">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45">
       <c r="A4" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -1073,55 +1073,55 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30">
       <c r="A5" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30">
       <c r="A7" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -1133,15 +1133,15 @@
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="45">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -1150,38 +1150,38 @@
         <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="45">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>17</v>
@@ -1190,557 +1190,557 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30">
       <c r="A14" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30">
       <c r="A15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30">
       <c r="A16" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="105">
       <c r="A17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="105">
       <c r="A18" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="90">
       <c r="A19" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="135">
       <c r="A20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="120">
       <c r="A21" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="120">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="D22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30">
       <c r="A23" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30">
       <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30">
       <c r="A27" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30">
       <c r="A28" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="E28" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="90">
       <c r="A29" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="45">
       <c r="A30" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="45">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45">
       <c r="A32" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45">
       <c r="A33" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>148</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30">
       <c r="A34" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="45">
       <c r="A35" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>154</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="45">
       <c r="A36" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="45">
       <c r="A37" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30">
       <c r="A38" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="45">
       <c r="A39" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/Input/redaction_template.xlsx
+++ b/Input/redaction_template.xlsx
@@ -76,21 +76,9 @@
     <t>variation_mensuelle_ipc_alim =0</t>
   </si>
   <si>
-    <t>Sur un mois, l'indice des prix des produits alimentaires a maintenu la même évolution en {lib_mois_courant} {annee_courante} par rapport à  {lib_mois_m1} {annee_m1}</t>
-  </si>
-  <si>
-    <t>Sur un mois, l'indice des prix des produits alimentaires a augumenté de {evol_alim_1mois}% en {lib_mois_courant} {annee_courante} par rapport à  {lib_mois_m1} {annee_m1}</t>
-  </si>
-  <si>
     <t>The consumer price index experienced an increase of {evol_alim_1mois}% during the month of  {lib_mois_courant} {annee_courante} compared to the previous month.</t>
   </si>
   <si>
-    <t>Sur un mois, l'indice des prix des produits alimentaires a diminué de {evol_alim_1mois}% en {lib_mois_courant} {annee_courante} par rapport à  {lib_mois_m1} {annee_m1}</t>
-  </si>
-  <si>
-    <t>The consumer price index experienced a decrease of {evol_alim_1mois}% during the month of  {lib_mois_courant} {annee_courante} compared to the previous month.</t>
-  </si>
-  <si>
     <t>variation_mensuelle_ipc_alim* nonalim &lt; 0</t>
   </si>
   <si>
@@ -100,9 +88,6 @@
     <t>variation_mensuelle_ipc_alim* nonalim = 0</t>
   </si>
   <si>
-    <t>De même</t>
-  </si>
-  <si>
     <t>En revanche,</t>
   </si>
   <si>
@@ -172,15 +157,6 @@
     <t>In  {lib_mois_courant} {annee_courante}, the national consumer price index increased by {evol_1mois}% compared to the previous month,</t>
   </si>
   <si>
-    <t>En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation des ménages de la {ville} a décru de {evol_1mois}% par rapport au mois précédent.</t>
-  </si>
-  <si>
-    <t>في شهر {lib_mois_courant } {annee_courante } انخفضت أسعار الاستهلاك على المستوى الوطني بنسبة ({evol_1mois}% )  خلال شهر واحد</t>
-  </si>
-  <si>
-    <t>In  {lib_mois_courant} {annee_courante}, the national consumer price index decreased by {evol_1mois}% compared to the previous month,</t>
-  </si>
-  <si>
     <t xml:space="preserve">En glissement annuel, il a accru de {evol_12mois}%. </t>
   </si>
   <si>
@@ -190,15 +166,6 @@
     <t xml:space="preserve"> while the consumer price index increased by {evol_12mois}% over a full year.</t>
   </si>
   <si>
-    <t>En glissement annuel, il a décru de {evol_12mois}%.</t>
-  </si>
-  <si>
-    <t>في حين انخفضت أسعار الاستهلاك بما يقارب  ({evol_12mois}% )  خلال سنة كاملة.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> while the consumer price index decreased by {evol_12mois}% over a full year.</t>
-  </si>
-  <si>
     <t>p03_plus</t>
   </si>
   <si>
@@ -302,22 +269,6 @@
   </si>
   <si>
     <t>p07</t>
-  </si>
-  <si>
-    <t>l’indice des prix des produits alimentaires
-a accru de {evol_alim_12mois}% en {lib_mois_courant} {annee_courante}, par rapport à {lib_mois_courant} {annee_m12}, sous l'effet de l’augmentation des
-prix  {liste_pdt_alim_12mois_plus}. Par ailleurs, la diminution des prix {liste_pdt_alim_12mois_moins} et la stagnation des prix  {liste_pdt_alim_12mois_neutre} n’ont pas affecté l’évolution
-générale.</t>
-  </si>
-  <si>
-    <t>l’indice des prix des produits alimentaires
-a baissé de {evol_alim_12mois}% en {lib_mois_courant} {annee_courante}, par rapport à {lib_mois_courant} {annee_m12}, sous l'effet de la diminution des
-prix  {liste_pdt_alim_12mois_moins}. Par ailleurs, l'augmentation des prix {liste_pdt_alim_12mois_plus} et la stagnation des prix  {liste_pdt_alim_12mois_neutre} n’ont pas affecté l’évolution générale.</t>
-  </si>
-  <si>
-    <t>l’indice des prix des produits alimentaires
-a maintenu la même évolution en {lib_mois_courant} {annee_courante}, par rapport à {lib_mois_courant} {annee_m12}, sous l'effet de la stagnation des
-prix  {liste_pdt_alim_12mois_neutre}. Par ailleurs, l'augmentation des prix {liste_pdt_alim_12mois_moins} et la diminution des prix  {liste_pdt_alim_12mois_neutre} n’ont pas affecté l’évolution générale.</t>
   </si>
   <si>
     <t>evol_alim_12mois&lt;0</t>
@@ -409,9 +360,6 @@
     <t>la variation annuelle de l'indice des produits non alimentaires a augmenté de {evol_non_alim_12mois}%.</t>
   </si>
   <si>
-    <t>la variation annuelle de l'indice des produits non alimentaires a diminué de {evol_non_alim_12mois}%.</t>
-  </si>
-  <si>
     <t>la variation annuelle de l'indice des produits non alimentaires a stagné.</t>
   </si>
   <si>
@@ -421,13 +369,7 @@
     <t>the annual variation in the non-food index increased by {evol_non_alim_12mois}%.</t>
   </si>
   <si>
-    <t>the annual variation in the non-food index decreased by {evol_non_alim_12mois}%.</t>
-  </si>
-  <si>
     <t>the annual variation in the non-food index stagnated</t>
-  </si>
-  <si>
-    <t>سجل التغير السنوي لمؤشر المواد غير الغذائية انخفاضا ب {evol_non_alim_12mois} %،</t>
   </si>
   <si>
     <t>سجل التغير السنوي لمؤشر المواد غير الغذائية ارتفاعا ب {evol_non_alim_12mois} %،</t>
@@ -497,9 +439,6 @@
     <t>p16_plus</t>
   </si>
   <si>
-    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a augmenté de {evol_1mois}% par rapport à {lib_mois_m1} {annee_m1}</t>
-  </si>
-  <si>
     <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } ارتفع الرقم الاستدلالي للأثمان عند الاستهلاك
 ب {evol_1mois} % مقارنة بشهر {lib_mois_m1} {annee_m1 } </t>
   </si>
@@ -507,9 +446,6 @@
     <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index increased by {evol_1mois}% compared to {lib_mois_m1} {annee_m1}</t>
   </si>
   <si>
-    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a diminué de {evol_1mois}% par rapport à {lib_mois_m1} {annee_m1}</t>
-  </si>
-  <si>
     <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } انخفظ الرقم الاستدلالي للأثمان عند الاستهلاك
 ب {evol_1mois} % مقارنة بشهر {lib_mois_m1} {annee_m1 } </t>
   </si>
@@ -526,9 +462,6 @@
     <t>evol_1mois = 0</t>
   </si>
   <si>
-    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a gardé la même valeur par rapport à {lib_mois_m1} {annee_m1}</t>
-  </si>
-  <si>
     <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } حافظ الرقم الاستدلالي للأثمان عند الاستهلاك
 على نفس القيمة مقارنة بشهر {lib_mois_m1 } {annee_m1 } </t>
   </si>
@@ -553,16 +486,6 @@
   </si>
   <si>
     <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index increased by {evol_12mois}% compared to {lib_mois_courant} {annee_m12}</t>
-  </si>
-  <si>
-    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index decreased by {evol_12mois}% compared to {lib_mois_courant} {annee_m12}</t>
-  </si>
-  <si>
-    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a décru de {evol_12mois}% par rapport à {lib_mois_courant} {annee_m12}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } انخفض الرقم الاستدلالي للأثمان عند الاستهلاك
-{evol_12mois} % مقارنة بشهر {lib_mois_courant } {annee_m12 } </t>
   </si>
   <si>
     <t>p17</t>
@@ -609,31 +532,275 @@
     </r>
   </si>
   <si>
-    <t>la variation mensuelle de l'indice des produits non alimentaires a accru de  {evol_non_alim_1mois}% en raison de la hausse des prix des divisions suivantes : {liste_div_non_alim_plus}. Aussi la baisse des prix {liste_div_non_alim_moins} et la stagnation des indices des autres
+    <t>La variation mensuelle de l'indice des produits non alimentaires a stagné suite à la stagnation des prix des divisions suivantes: {liste_div_non_alim_neutre}.Aussi la hausse des prix {liste_div_non_alim_plus} et la baisse des prix {liste_div_non_alim_moins} n’ont pas impacté l'évolution générale.</t>
+  </si>
+  <si>
+    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد الغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  .</t>
+  </si>
+  <si>
+    <r>
+      <t>la variation mensuelle de l'indice des produits non alimentaires a decru de  {evol_non_alim_1mois}% en raison de la baisse des prix des divisions suivantes: {liste_div_non_alim_moins}. Aussi la hausse hausse des prix {liste_div_non_alim_plus}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Ainsi que,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> la stagnation des indices des autres
 divisions n’ont pas impacté l'évolution générale.</t>
-  </si>
-  <si>
-    <t>la variation mensuelle de l'indice des produits non alimentaires a decru de  {evol_non_alim_1mois}% en raison de la baisse des prix des divisions suivantes: {liste_div_non_alim_moins}. Aussi la hausse hausse des prix {liste_div_non_alim_plus} et la stagnation des indices des autres
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a augmenté de {evol_1mois}%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>par rapport à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {lib_mois_m1} {annee_m1}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a diminué de {evol_1mois}% </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>par rapport à</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {lib_mois_m1} {annee_m1}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lecture: En {lib_mois_courant} {annee_courante}, </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>l'indice des prix à la consommation a gardé la même valeur</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> par rapport à {lib_mois_m1} {annee_m1}</t>
+    </r>
+  </si>
+  <si>
+    <t>En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation des ménages de la {ville} a décru de {abs(evol_1mois)}% par rapport au mois précédent.</t>
+  </si>
+  <si>
+    <t>In  {lib_mois_courant} {annee_courante}, the national consumer price index decreased by {abs(evol_1mois)}% compared to the previous month,</t>
+  </si>
+  <si>
+    <t>En glissement annuel, il a décru de {abs(evol_12mois)}%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> while the consumer price index decreased by {abs(evol_12mois)}% over a full year.</t>
+  </si>
+  <si>
+    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد الغذائية ب 
+{evol_alim_1mois}%
+  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 } .{annee_m1 }</t>
+  </si>
+  <si>
+    <t>The consumer price index experienced a decrease of {abs(evol_alim_1mois)}% during the month of  {lib_mois_courant} {annee_courante} compared to the previous month.</t>
+  </si>
+  <si>
+    <t>la variation annuelle de l'indice des produits non alimentaires a diminué de {abs(evol_non_alim_12mois)}%.</t>
+  </si>
+  <si>
+    <t>the annual variation in the non-food index decreased by {abs(evol_non_alim_12mois)}%.</t>
+  </si>
+  <si>
+    <t>Lecture: En {lib_mois_courant} {annee_courante}, l'indice des prix à la consommation a décru de {abs(evol_12mois)}% par rapport à {lib_mois_courant} {annee_m12}</t>
+  </si>
+  <si>
+    <t>Reading: In {lib_mois_courant} {annee_courante}, the consumer price index decreased by {abs(evol_12mois)}% compared to {lib_mois_courant} {annee_m12}</t>
+  </si>
+  <si>
+    <t>في حين انخفضت أسعار الاستهلاك بما يقارب  ({abs(evol_12mois)}'% )  خلال سنة كاملة.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قراءة: في {lib_mois_courant } {annee_courante } انخفض الرقم الاستدلالي للأثمان عند الاستهلاك
+{abs(evol_12mois)}'% مقارنة بشهر {lib_mois_courant } {annee_m12 } </t>
+  </si>
+  <si>
+    <t>في شهر {lib_mois_courant } {annee_courante } انخفضت أسعار الاستهلاك على المستوى الوطني بنسبة ({abs(evol_1mois)}'% )  خلال شهر واحد</t>
+  </si>
+  <si>
+    <t>على المستوى الشهري انخفض الرقم الاستدلالي للمواد الغذائية ب {abs(evo_alim_1mois)}'% في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 }  .{annee_m1 }</t>
+  </si>
+  <si>
+    <t>سجل التغير السنوي لمؤشر المواد غير الغذائية انخفاضا ب {abs(evol_non_alim_12mois)}'%،</t>
+  </si>
+  <si>
+    <r>
+      <t>l'indice des prix des produits alimentaires a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> augmenté</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> de {evol_alim_1mois}% en {lib_mois_courant} {annee_courante} par rapport à  {lib_mois_m1} {annee_m1},</t>
+    </r>
+  </si>
+  <si>
+    <t>l'indice des prix des produits alimentaires a diminué de {abs(evol_alim_1mois)}% en {lib_mois_courant} {annee_courante} par rapport à  {lib_mois_m1} {annee_m1},</t>
+  </si>
+  <si>
+    <t>l'indice des prix des produits alimentaires a maintenu la même évolution en {lib_mois_courant} {annee_courante} par rapport à  {lib_mois_m1} {annee_m1},</t>
+  </si>
+  <si>
+    <t>كما،</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">la variation mensuelle de l'indice des produits non alimentaires a accru de  {evol_non_alim_1mois}% en raison de la hausse des prix des divisions suivantes: {liste_div_non_alim_plus}. Aussi la baisse des prix </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">des divisions suivantes : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{liste_div_non_alim_moins}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Ainsi que,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> la stagnation des indices des autres
 divisions n’ont pas impacté l'évolution générale.</t>
-  </si>
-  <si>
-    <t>La variation mensuelle de l'indice des produits non alimentaires a stagné suite à la stagnation des prix des divisions suivantes: {liste_div_non_alim_neutre}.Aussi la hausse des prix {liste_div_non_alim_plus} et la baisse des prix {liste_div_non_alim_moins} n’ont pas impacté l'évolution générale.</t>
-  </si>
-  <si>
-    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد الغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 } .{annee_m1 }</t>
-  </si>
-  <si>
-    <t>على المستوى الشهري انخفض الرقم الاستدلالي للمواد الغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  {lib_mois_m1 }  .{annee_m1 }</t>
-  </si>
-  <si>
-    <t>على المستوى الشهري ارتفع الرقم الاستدلالي للمواد الغذائية ب {evol_alim_1mois}%  في شهر {lib_mois_courant } {annee_courante } مقارنة بشهر  .</t>
+    </r>
+  </si>
+  <si>
+    <t>l’indice des prix des produits alimentaires
+a accru de {evol_alim_12mois}% en {lib_mois_courant} {annee_courante} par rapport à {lib_mois_courant} {annee_m12}, sous l'effet de l’augmentation des
+prix  {liste_pdt_alim_12mois_plus}. Par ailleurs, la diminution des prix {liste_pdt_alim_12mois_moins} et la stagnation des prix  {liste_pdt_alim_12mois_neutre} n’ont pas affecté l’évolution
+générale.</t>
+  </si>
+  <si>
+    <t>l’indice des prix des produits alimentaires
+a baissé de {evol_alim_12mois}% en {lib_mois_courant} {annee_courante} par rapport à {lib_mois_courant} {annee_m12}, sous l'effet de la diminution des
+prix  {liste_pdt_alim_12mois_moins}. Par ailleurs, l'augmentation des prix {liste_pdt_alim_12mois_plus} et la stagnation des prix  {liste_pdt_alim_12mois_neutre} n’ont pas affecté l’évolution générale.</t>
+  </si>
+  <si>
+    <t>l’indice des prix des produits alimentaires
+a maintenu la même évolution en {lib_mois_courant} {annee_courante} par rapport à {lib_mois_courant} {annee_m12}, sous l'effet de la stagnation des
+prix  {liste_pdt_alim_12mois_neutre}. Par ailleurs, l'augmentation des prix {liste_pdt_alim_12mois_moins} et la diminution des prix  {liste_pdt_alim_12mois_neutre} n’ont pas affecté l’évolution générale.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +838,21 @@
       <color rgb="FF000000"/>
       <name val="TimesNewRomanPS-BoldMT"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -692,7 +874,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -703,6 +885,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -990,7 +1175,7 @@
     <col min="1" max="1" width="8.85546875" style="1"/>
     <col min="2" max="2" width="35.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="55" style="1" customWidth="1"/>
+    <col min="4" max="4" width="57.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="60.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="56.42578125" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.85546875" style="1"/>
@@ -998,7 +1183,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -1018,50 +1203,50 @@
     </row>
     <row r="2" spans="1:6" ht="45">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="45">
       <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>176</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45">
       <c r="A4" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
@@ -1073,55 +1258,55 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="30">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>174</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>58</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>12</v>
@@ -1133,614 +1318,614 @@
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="45">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="60">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="45">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="45">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30">
       <c r="A14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30">
       <c r="A15" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30">
       <c r="A16" s="1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="105">
       <c r="A17" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="105">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="90">
       <c r="A19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="135">
       <c r="A20" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>94</v>
+        <v>184</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="120">
       <c r="A21" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>95</v>
+        <v>185</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="120">
       <c r="A22" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="30">
       <c r="A23" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30">
       <c r="A26" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30">
       <c r="A27" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30">
       <c r="A28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="75">
+      <c r="A29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="E29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30">
+      <c r="A30" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="90">
-      <c r="A29" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="45">
-      <c r="A30" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="45">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="45">
       <c r="A32" s="1" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="45">
       <c r="A33" s="1" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30">
       <c r="A34" s="1" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="45">
       <c r="A35" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="45">
       <c r="A36" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="45">
       <c r="A37" s="1" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>161</v>
+        <v>141</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30">
       <c r="A38" s="1" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="45">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="30">
       <c r="A39" s="1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
